--- a/backend/excel-files/sample_30_students.xlsx
+++ b/backend/excel-files/sample_30_students.xlsx
@@ -428,7 +428,7 @@
         <v>Cohort</v>
       </c>
       <c r="G1" t="str">
-        <v>Academic Year</v>
+        <v>Admission Year</v>
       </c>
     </row>
     <row r="2">
@@ -450,8 +450,8 @@
       <c r="F2" t="str">
         <v>January</v>
       </c>
-      <c r="G2" t="str">
-        <v>2024/2025</v>
+      <c r="G2">
+        <v>2022</v>
       </c>
     </row>
     <row r="3">
@@ -473,8 +473,8 @@
       <c r="F3" t="str">
         <v>July</v>
       </c>
-      <c r="G3" t="str">
-        <v>2024/2025</v>
+      <c r="G3">
+        <v>2022</v>
       </c>
     </row>
     <row r="4">
@@ -496,8 +496,8 @@
       <c r="F4" t="str">
         <v>January</v>
       </c>
-      <c r="G4" t="str">
-        <v>2024/2025</v>
+      <c r="G4">
+        <v>2022</v>
       </c>
     </row>
     <row r="5">
@@ -519,8 +519,8 @@
       <c r="F5" t="str">
         <v>July</v>
       </c>
-      <c r="G5" t="str">
-        <v>2024/2025</v>
+      <c r="G5">
+        <v>2022</v>
       </c>
     </row>
     <row r="6">
@@ -542,8 +542,8 @@
       <c r="F6" t="str">
         <v>January</v>
       </c>
-      <c r="G6" t="str">
-        <v>2024/2025</v>
+      <c r="G6">
+        <v>2022</v>
       </c>
     </row>
     <row r="7">
@@ -565,8 +565,8 @@
       <c r="F7" t="str">
         <v>July</v>
       </c>
-      <c r="G7" t="str">
-        <v>2024/2025</v>
+      <c r="G7">
+        <v>2022</v>
       </c>
     </row>
     <row r="8">
@@ -588,8 +588,8 @@
       <c r="F8" t="str">
         <v>January</v>
       </c>
-      <c r="G8" t="str">
-        <v>2024/2025</v>
+      <c r="G8">
+        <v>2022</v>
       </c>
     </row>
     <row r="9">
@@ -611,8 +611,8 @@
       <c r="F9" t="str">
         <v>July</v>
       </c>
-      <c r="G9" t="str">
-        <v>2024/2025</v>
+      <c r="G9">
+        <v>2022</v>
       </c>
     </row>
     <row r="10">
@@ -634,8 +634,8 @@
       <c r="F10" t="str">
         <v>January</v>
       </c>
-      <c r="G10" t="str">
-        <v>2026/2027</v>
+      <c r="G10">
+        <v>2024</v>
       </c>
     </row>
     <row r="11">
@@ -657,8 +657,8 @@
       <c r="F11" t="str">
         <v>July</v>
       </c>
-      <c r="G11" t="str">
-        <v>2026/2027</v>
+      <c r="G11">
+        <v>2024</v>
       </c>
     </row>
     <row r="12">
@@ -680,8 +680,8 @@
       <c r="F12" t="str">
         <v>January</v>
       </c>
-      <c r="G12" t="str">
-        <v>2026/2027</v>
+      <c r="G12">
+        <v>2024</v>
       </c>
     </row>
     <row r="13">
@@ -703,8 +703,8 @@
       <c r="F13" t="str">
         <v>July</v>
       </c>
-      <c r="G13" t="str">
-        <v>2026/2027</v>
+      <c r="G13">
+        <v>2024</v>
       </c>
     </row>
     <row r="14">
@@ -726,8 +726,8 @@
       <c r="F14" t="str">
         <v>January</v>
       </c>
-      <c r="G14" t="str">
-        <v>2026/2027</v>
+      <c r="G14">
+        <v>2024</v>
       </c>
     </row>
     <row r="15">
@@ -749,8 +749,8 @@
       <c r="F15" t="str">
         <v>July</v>
       </c>
-      <c r="G15" t="str">
-        <v>2026/2027</v>
+      <c r="G15">
+        <v>2024</v>
       </c>
     </row>
     <row r="16">
@@ -772,8 +772,8 @@
       <c r="F16" t="str">
         <v>January</v>
       </c>
-      <c r="G16" t="str">
-        <v>2026/2027</v>
+      <c r="G16">
+        <v>2024</v>
       </c>
     </row>
     <row r="17">
@@ -795,8 +795,8 @@
       <c r="F17" t="str">
         <v>July</v>
       </c>
-      <c r="G17" t="str">
-        <v>2026/2027</v>
+      <c r="G17">
+        <v>2024</v>
       </c>
     </row>
     <row r="18">
@@ -818,8 +818,8 @@
       <c r="F18" t="str">
         <v>January</v>
       </c>
-      <c r="G18" t="str">
-        <v>2026/2027</v>
+      <c r="G18">
+        <v>2024</v>
       </c>
     </row>
     <row r="19">
@@ -841,8 +841,8 @@
       <c r="F19" t="str">
         <v>July</v>
       </c>
-      <c r="G19" t="str">
-        <v>2026/2027</v>
+      <c r="G19">
+        <v>2024</v>
       </c>
     </row>
     <row r="20">
@@ -864,8 +864,8 @@
       <c r="F20" t="str">
         <v>January</v>
       </c>
-      <c r="G20" t="str">
-        <v>2026/2027</v>
+      <c r="G20">
+        <v>2024</v>
       </c>
     </row>
     <row r="21">
@@ -887,8 +887,8 @@
       <c r="F21" t="str">
         <v>July</v>
       </c>
-      <c r="G21" t="str">
-        <v>2026/2027</v>
+      <c r="G21">
+        <v>2024</v>
       </c>
     </row>
     <row r="22">
@@ -910,8 +910,8 @@
       <c r="F22" t="str">
         <v>January</v>
       </c>
-      <c r="G22" t="str">
-        <v>2026/2027</v>
+      <c r="G22">
+        <v>2024</v>
       </c>
     </row>
     <row r="23">
@@ -933,8 +933,8 @@
       <c r="F23" t="str">
         <v>July</v>
       </c>
-      <c r="G23" t="str">
-        <v>2026/2027</v>
+      <c r="G23">
+        <v>2024</v>
       </c>
     </row>
     <row r="24">
@@ -956,8 +956,8 @@
       <c r="F24" t="str">
         <v>January</v>
       </c>
-      <c r="G24" t="str">
-        <v>2026/2027</v>
+      <c r="G24">
+        <v>2024</v>
       </c>
     </row>
     <row r="25">
@@ -979,8 +979,8 @@
       <c r="F25" t="str">
         <v>July</v>
       </c>
-      <c r="G25" t="str">
-        <v>2026/2027</v>
+      <c r="G25">
+        <v>2024</v>
       </c>
     </row>
     <row r="26">
@@ -1002,8 +1002,8 @@
       <c r="F26" t="str">
         <v>January</v>
       </c>
-      <c r="G26" t="str">
-        <v>2026/2027</v>
+      <c r="G26">
+        <v>2024</v>
       </c>
     </row>
     <row r="27">
@@ -1025,8 +1025,8 @@
       <c r="F27" t="str">
         <v>July</v>
       </c>
-      <c r="G27" t="str">
-        <v>2026/2027</v>
+      <c r="G27">
+        <v>2024</v>
       </c>
     </row>
     <row r="28">
@@ -1048,8 +1048,8 @@
       <c r="F28" t="str">
         <v>January</v>
       </c>
-      <c r="G28" t="str">
-        <v>2026/2027</v>
+      <c r="G28">
+        <v>2024</v>
       </c>
     </row>
     <row r="29">
@@ -1071,8 +1071,8 @@
       <c r="F29" t="str">
         <v>July</v>
       </c>
-      <c r="G29" t="str">
-        <v>2026/2027</v>
+      <c r="G29">
+        <v>2024</v>
       </c>
     </row>
     <row r="30">
@@ -1094,8 +1094,8 @@
       <c r="F30" t="str">
         <v>January</v>
       </c>
-      <c r="G30" t="str">
-        <v>2026/2027</v>
+      <c r="G30">
+        <v>2024</v>
       </c>
     </row>
     <row r="31">
@@ -1117,8 +1117,8 @@
       <c r="F31" t="str">
         <v>July</v>
       </c>
-      <c r="G31" t="str">
-        <v>2026/2027</v>
+      <c r="G31">
+        <v>2024</v>
       </c>
     </row>
   </sheetData>

--- a/backend/excel-files/sample_30_students.xlsx
+++ b/backend/excel-files/sample_30_students.xlsx
@@ -436,10 +436,10 @@
         <v>Kwame Mensah</v>
       </c>
       <c r="B2" t="str">
-        <v>UMaT/PG/0001/22</v>
+        <v>UMaT/PG/0301/22</v>
       </c>
       <c r="C2" t="str">
-        <v>kwame.mensah0001@umat.edu.gh</v>
+        <v>kwame.mensah.s0301@umat.edu.gh</v>
       </c>
       <c r="D2" t="str">
         <v>Computer Science and Engineering MPhil</v>
@@ -459,10 +459,10 @@
         <v>Akosua Asante</v>
       </c>
       <c r="B3" t="str">
-        <v>UMaT/PG/0002/22</v>
+        <v>UMaT/PG/0302/22</v>
       </c>
       <c r="C3" t="str">
-        <v>akosua.asante0002@umat.edu.gh</v>
+        <v>akosua.asante.s0302@umat.edu.gh</v>
       </c>
       <c r="D3" t="str">
         <v>Electrical and Electronic Engineering MSc</v>
@@ -482,10 +482,10 @@
         <v>Kofi Boateng</v>
       </c>
       <c r="B4" t="str">
-        <v>UMaT/PG/0003/22</v>
+        <v>UMaT/PG/0303/22</v>
       </c>
       <c r="C4" t="str">
-        <v>kofi.boateng0003@umat.edu.gh</v>
+        <v>kofi.boateng.s0303@umat.edu.gh</v>
       </c>
       <c r="D4" t="str">
         <v>Mining Engineering MPhil</v>
@@ -505,10 +505,10 @@
         <v>Yaa Appiah</v>
       </c>
       <c r="B5" t="str">
-        <v>UMaT/PG/0004/22</v>
+        <v>UMaT/PG/0304/22</v>
       </c>
       <c r="C5" t="str">
-        <v>yaa.appiah0004@umat.edu.gh</v>
+        <v>yaa.appiah.s0304@umat.edu.gh</v>
       </c>
       <c r="D5" t="str">
         <v>Geomatic Engineering MSc</v>
@@ -528,10 +528,10 @@
         <v>Kojo Osei</v>
       </c>
       <c r="B6" t="str">
-        <v>UMaT/PG/0005/22</v>
+        <v>UMaT/PG/0305/22</v>
       </c>
       <c r="C6" t="str">
-        <v>kojo.osei0005@umat.edu.gh</v>
+        <v>kojo.osei.s0305@umat.edu.gh</v>
       </c>
       <c r="D6" t="str">
         <v>Mechanical Engineering MPhil</v>
@@ -551,10 +551,10 @@
         <v>Adwoa Frimpong</v>
       </c>
       <c r="B7" t="str">
-        <v>UMaT/PG/0006/22</v>
+        <v>UMaT/PG/0306/22</v>
       </c>
       <c r="C7" t="str">
-        <v>adwoa.frimpong0006@umat.edu.gh</v>
+        <v>adwoa.frimpong.s0306@umat.edu.gh</v>
       </c>
       <c r="D7" t="str">
         <v>Petroleum Engineering MSc</v>
@@ -574,10 +574,10 @@
         <v>Yaw Sarpong</v>
       </c>
       <c r="B8" t="str">
-        <v>UMaT/PG/0007/22</v>
+        <v>UMaT/PG/0307/22</v>
       </c>
       <c r="C8" t="str">
-        <v>yaw.sarpong0007@umat.edu.gh</v>
+        <v>yaw.sarpong.s0307@umat.edu.gh</v>
       </c>
       <c r="D8" t="str">
         <v>Geological Engineering MPhil</v>
@@ -597,10 +597,10 @@
         <v>Abena Owusu</v>
       </c>
       <c r="B9" t="str">
-        <v>UMaT/PG/0008/22</v>
+        <v>UMaT/PG/0308/22</v>
       </c>
       <c r="C9" t="str">
-        <v>abena.owusu0008@umat.edu.gh</v>
+        <v>abena.owusu.s0308@umat.edu.gh</v>
       </c>
       <c r="D9" t="str">
         <v>Minerals Engineering MSc</v>
@@ -620,10 +620,10 @@
         <v>Kwabena Agyemang</v>
       </c>
       <c r="B10" t="str">
-        <v>UMaT/PG/0009/24</v>
+        <v>UMaT/PG/0309/24</v>
       </c>
       <c r="C10" t="str">
-        <v>kwabena.agyemang0009@umat.edu.gh</v>
+        <v>kwabena.agyemang.s0309@umat.edu.gh</v>
       </c>
       <c r="D10" t="str">
         <v>Mathematical Sciences MPhil</v>
@@ -643,10 +643,10 @@
         <v>Akua Darko</v>
       </c>
       <c r="B11" t="str">
-        <v>UMaT/PG/0010/24</v>
+        <v>UMaT/PG/0310/24</v>
       </c>
       <c r="C11" t="str">
-        <v>akua.darko0010@umat.edu.gh</v>
+        <v>akua.darko.s0310@umat.edu.gh</v>
       </c>
       <c r="D11" t="str">
         <v>Management Studies MSc</v>
@@ -666,10 +666,10 @@
         <v>Kwesi Annan</v>
       </c>
       <c r="B12" t="str">
-        <v>UMaT/PG/0011/24</v>
+        <v>UMaT/PG/0311/24</v>
       </c>
       <c r="C12" t="str">
-        <v>kwesi.annan0011@umat.edu.gh</v>
+        <v>kwesi.annan.s0311@umat.edu.gh</v>
       </c>
       <c r="D12" t="str">
         <v>Environmental and Safety Engineering MPhil</v>
@@ -689,10 +689,10 @@
         <v>Adjoa Nkrumah</v>
       </c>
       <c r="B13" t="str">
-        <v>UMaT/PG/0012/24</v>
+        <v>UMaT/PG/0312/24</v>
       </c>
       <c r="C13" t="str">
-        <v>adjoa.nkrumah0012@umat.edu.gh</v>
+        <v>adjoa.nkrumah.s0312@umat.edu.gh</v>
       </c>
       <c r="D13" t="str">
         <v>Computer Science and Engineering MSc</v>
@@ -712,10 +712,10 @@
         <v>Ama Acheampong</v>
       </c>
       <c r="B14" t="str">
-        <v>UMaT/PG/0013/24</v>
+        <v>UMaT/PG/0313/24</v>
       </c>
       <c r="C14" t="str">
-        <v>ama.acheampong0013@umat.edu.gh</v>
+        <v>ama.acheampong.s0313@umat.edu.gh</v>
       </c>
       <c r="D14" t="str">
         <v>Electrical and Electronic Engineering MPhil</v>
@@ -735,10 +735,10 @@
         <v>Efua Ofori</v>
       </c>
       <c r="B15" t="str">
-        <v>UMaT/PG/0014/24</v>
+        <v>UMaT/PG/0314/24</v>
       </c>
       <c r="C15" t="str">
-        <v>efua.ofori0014@umat.edu.gh</v>
+        <v>efua.ofori.s0314@umat.edu.gh</v>
       </c>
       <c r="D15" t="str">
         <v>Mining Engineering MSc</v>
@@ -758,10 +758,10 @@
         <v>Kobina Ansah</v>
       </c>
       <c r="B16" t="str">
-        <v>UMaT/PG/0015/24</v>
+        <v>UMaT/PG/0315/24</v>
       </c>
       <c r="C16" t="str">
-        <v>kobina.ansah0015@umat.edu.gh</v>
+        <v>kobina.ansah.s0315@umat.edu.gh</v>
       </c>
       <c r="D16" t="str">
         <v>Geomatic Engineering MPhil</v>
@@ -781,10 +781,10 @@
         <v>Ekua Addo</v>
       </c>
       <c r="B17" t="str">
-        <v>UMaT/PG/0016/24</v>
+        <v>UMaT/PG/0316/24</v>
       </c>
       <c r="C17" t="str">
-        <v>ekua.addo0016@umat.edu.gh</v>
+        <v>ekua.addo.s0316@umat.edu.gh</v>
       </c>
       <c r="D17" t="str">
         <v>Mechanical Engineering MSc</v>
@@ -804,10 +804,10 @@
         <v>Esi Boakye</v>
       </c>
       <c r="B18" t="str">
-        <v>UMaT/PG/0017/24</v>
+        <v>UMaT/PG/0317/24</v>
       </c>
       <c r="C18" t="str">
-        <v>esi.boakye0017@umat.edu.gh</v>
+        <v>esi.boakye.s0317@umat.edu.gh</v>
       </c>
       <c r="D18" t="str">
         <v>Petroleum Engineering MPhil</v>
@@ -827,10 +827,10 @@
         <v>Afia Opoku</v>
       </c>
       <c r="B19" t="str">
-        <v>UMaT/PG/0018/24</v>
+        <v>UMaT/PG/0318/24</v>
       </c>
       <c r="C19" t="str">
-        <v>afia.opoku0018@umat.edu.gh</v>
+        <v>afia.opoku.s0318@umat.edu.gh</v>
       </c>
       <c r="D19" t="str">
         <v>Geological Engineering MSc</v>
@@ -850,10 +850,10 @@
         <v>Kwadwo Gyasi</v>
       </c>
       <c r="B20" t="str">
-        <v>UMaT/PG/0019/24</v>
+        <v>UMaT/PG/0319/24</v>
       </c>
       <c r="C20" t="str">
-        <v>kwadwo.gyasi0019@umat.edu.gh</v>
+        <v>kwadwo.gyasi.s0319@umat.edu.gh</v>
       </c>
       <c r="D20" t="str">
         <v>Minerals Engineering MPhil</v>
@@ -873,10 +873,10 @@
         <v>Ebo Danquah</v>
       </c>
       <c r="B21" t="str">
-        <v>UMaT/PG/0020/24</v>
+        <v>UMaT/PG/0320/24</v>
       </c>
       <c r="C21" t="str">
-        <v>ebo.danquah0020@umat.edu.gh</v>
+        <v>ebo.danquah.s0320@umat.edu.gh</v>
       </c>
       <c r="D21" t="str">
         <v>Mathematical Sciences MSc</v>
@@ -896,10 +896,10 @@
         <v>Ato Afriyie</v>
       </c>
       <c r="B22" t="str">
-        <v>UMaT/PG/0021/24</v>
+        <v>UMaT/PG/0321/24</v>
       </c>
       <c r="C22" t="str">
-        <v>ato.afriyie0021@umat.edu.gh</v>
+        <v>ato.afriyie.s0321@umat.edu.gh</v>
       </c>
       <c r="D22" t="str">
         <v>Management Studies MBA</v>
@@ -919,10 +919,10 @@
         <v>Kodwo Amoah</v>
       </c>
       <c r="B23" t="str">
-        <v>UMaT/PG/0022/24</v>
+        <v>UMaT/PG/0322/24</v>
       </c>
       <c r="C23" t="str">
-        <v>kodwo.amoah0022@umat.edu.gh</v>
+        <v>kodwo.amoah.s0322@umat.edu.gh</v>
       </c>
       <c r="D23" t="str">
         <v>Environmental and Safety Engineering MSc</v>
@@ -942,10 +942,10 @@
         <v>Araba Yeboah</v>
       </c>
       <c r="B24" t="str">
-        <v>UMaT/PG/0023/24</v>
+        <v>UMaT/PG/0323/24</v>
       </c>
       <c r="C24" t="str">
-        <v>araba.yeboah0023@umat.edu.gh</v>
+        <v>araba.yeboah.s0323@umat.edu.gh</v>
       </c>
       <c r="D24" t="str">
         <v>Computer Science and Engineering MPhil</v>
@@ -965,10 +965,10 @@
         <v>Panyin Amankwah</v>
       </c>
       <c r="B25" t="str">
-        <v>UMaT/PG/0024/24</v>
+        <v>UMaT/PG/0324/24</v>
       </c>
       <c r="C25" t="str">
-        <v>panyin.amankwah0024@umat.edu.gh</v>
+        <v>panyin.amankwah.s0324@umat.edu.gh</v>
       </c>
       <c r="D25" t="str">
         <v>Electrical and Electronic Engineering MSc</v>
@@ -988,10 +988,10 @@
         <v>Kakra Adjei</v>
       </c>
       <c r="B26" t="str">
-        <v>UMaT/PG/0025/24</v>
+        <v>UMaT/PG/0325/24</v>
       </c>
       <c r="C26" t="str">
-        <v>kakra.adjei0025@umat.edu.gh</v>
+        <v>kakra.adjei.s0325@umat.edu.gh</v>
       </c>
       <c r="D26" t="str">
         <v>Mining Engineering MPhil</v>
@@ -1011,10 +1011,10 @@
         <v>Mansa Agyei</v>
       </c>
       <c r="B27" t="str">
-        <v>UMaT/PG/0026/24</v>
+        <v>UMaT/PG/0326/24</v>
       </c>
       <c r="C27" t="str">
-        <v>mansa.agyei0026@umat.edu.gh</v>
+        <v>mansa.agyei.s0326@umat.edu.gh</v>
       </c>
       <c r="D27" t="str">
         <v>Geomatic Engineering MSc</v>
@@ -1034,10 +1034,10 @@
         <v>Serwa Akuffo</v>
       </c>
       <c r="B28" t="str">
-        <v>UMaT/PG/0027/24</v>
+        <v>UMaT/PG/0327/24</v>
       </c>
       <c r="C28" t="str">
-        <v>serwa.akuffo0027@umat.edu.gh</v>
+        <v>serwa.akuffo.s0327@umat.edu.gh</v>
       </c>
       <c r="D28" t="str">
         <v>Mechanical Engineering MPhil</v>
@@ -1057,10 +1057,10 @@
         <v>Nana Wiredu</v>
       </c>
       <c r="B29" t="str">
-        <v>UMaT/PG/0028/24</v>
+        <v>UMaT/PG/0328/24</v>
       </c>
       <c r="C29" t="str">
-        <v>nana.wiredu0028@umat.edu.gh</v>
+        <v>nana.wiredu.s0328@umat.edu.gh</v>
       </c>
       <c r="D29" t="str">
         <v>Petroleum Engineering MSc</v>
@@ -1080,10 +1080,10 @@
         <v>Kwaku Quaye</v>
       </c>
       <c r="B30" t="str">
-        <v>UMaT/PG/0029/24</v>
+        <v>UMaT/PG/0329/24</v>
       </c>
       <c r="C30" t="str">
-        <v>kwaku.quaye0029@umat.edu.gh</v>
+        <v>kwaku.quaye.s0329@umat.edu.gh</v>
       </c>
       <c r="D30" t="str">
         <v>Geological Engineering MPhil</v>
@@ -1103,10 +1103,10 @@
         <v>Afi Tetteh</v>
       </c>
       <c r="B31" t="str">
-        <v>UMaT/PG/0030/24</v>
+        <v>UMaT/PG/0330/24</v>
       </c>
       <c r="C31" t="str">
-        <v>afi.tetteh0030@umat.edu.gh</v>
+        <v>afi.tetteh.s0330@umat.edu.gh</v>
       </c>
       <c r="D31" t="str">
         <v>Minerals Engineering MSc</v>

--- a/backend/excel-files/sample_30_students.xlsx
+++ b/backend/excel-files/sample_30_students.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -406,6 +406,7 @@
     <col min="5" max="5" width="40.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -430,6 +431,9 @@
       <c r="G1" t="str">
         <v>Admission Year</v>
       </c>
+      <c r="H1" t="str">
+        <v>Phone Number</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -453,6 +457,9 @@
       <c r="G2">
         <v>2022</v>
       </c>
+      <c r="H2" t="str">
+        <v>0249690360</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -476,6 +483,9 @@
       <c r="G3">
         <v>2022</v>
       </c>
+      <c r="H3" t="str">
+        <v>0202930167</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -499,6 +509,9 @@
       <c r="G4">
         <v>2022</v>
       </c>
+      <c r="H4" t="str">
+        <v>0271632876</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -522,6 +535,9 @@
       <c r="G5">
         <v>2022</v>
       </c>
+      <c r="H5" t="str">
+        <v>0507143834</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -545,6 +561,9 @@
       <c r="G6">
         <v>2022</v>
       </c>
+      <c r="H6" t="str">
+        <v>0553549073</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -568,6 +587,9 @@
       <c r="G7">
         <v>2022</v>
       </c>
+      <c r="H7" t="str">
+        <v>0277225454</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -591,6 +613,9 @@
       <c r="G8">
         <v>2022</v>
       </c>
+      <c r="H8" t="str">
+        <v>0209533102</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -614,6 +639,9 @@
       <c r="G9">
         <v>2022</v>
       </c>
+      <c r="H9" t="str">
+        <v>0568499196</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -637,6 +665,9 @@
       <c r="G10">
         <v>2024</v>
       </c>
+      <c r="H10" t="str">
+        <v>0201204249</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -660,6 +691,9 @@
       <c r="G11">
         <v>2024</v>
       </c>
+      <c r="H11" t="str">
+        <v>0248555127</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -683,6 +717,9 @@
       <c r="G12">
         <v>2024</v>
       </c>
+      <c r="H12" t="str">
+        <v>0548537748</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -706,6 +743,9 @@
       <c r="G13">
         <v>2024</v>
       </c>
+      <c r="H13" t="str">
+        <v>0597127539</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -729,6 +769,9 @@
       <c r="G14">
         <v>2024</v>
       </c>
+      <c r="H14" t="str">
+        <v>0544263209</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -752,6 +795,9 @@
       <c r="G15">
         <v>2024</v>
       </c>
+      <c r="H15" t="str">
+        <v>0565975654</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -775,6 +821,9 @@
       <c r="G16">
         <v>2024</v>
       </c>
+      <c r="H16" t="str">
+        <v>0561466551</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -798,6 +847,9 @@
       <c r="G17">
         <v>2024</v>
       </c>
+      <c r="H17" t="str">
+        <v>0548554554</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -821,6 +873,9 @@
       <c r="G18">
         <v>2024</v>
       </c>
+      <c r="H18" t="str">
+        <v>0276071602</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -844,6 +899,9 @@
       <c r="G19">
         <v>2024</v>
       </c>
+      <c r="H19" t="str">
+        <v>0245999699</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -867,6 +925,9 @@
       <c r="G20">
         <v>2024</v>
       </c>
+      <c r="H20" t="str">
+        <v>0566286828</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -890,6 +951,9 @@
       <c r="G21">
         <v>2024</v>
       </c>
+      <c r="H21" t="str">
+        <v>0271404331</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -913,6 +977,9 @@
       <c r="G22">
         <v>2024</v>
       </c>
+      <c r="H22" t="str">
+        <v>0268592825</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -936,6 +1003,9 @@
       <c r="G23">
         <v>2024</v>
       </c>
+      <c r="H23" t="str">
+        <v>0569365189</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -959,6 +1029,9 @@
       <c r="G24">
         <v>2024</v>
       </c>
+      <c r="H24" t="str">
+        <v>0245043130</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -982,6 +1055,9 @@
       <c r="G25">
         <v>2024</v>
       </c>
+      <c r="H25" t="str">
+        <v>0552811767</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1005,6 +1081,9 @@
       <c r="G26">
         <v>2024</v>
       </c>
+      <c r="H26" t="str">
+        <v>0279785145</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1028,6 +1107,9 @@
       <c r="G27">
         <v>2024</v>
       </c>
+      <c r="H27" t="str">
+        <v>0572392503</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1051,6 +1133,9 @@
       <c r="G28">
         <v>2024</v>
       </c>
+      <c r="H28" t="str">
+        <v>0244213382</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1074,6 +1159,9 @@
       <c r="G29">
         <v>2024</v>
       </c>
+      <c r="H29" t="str">
+        <v>0598647284</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1097,6 +1185,9 @@
       <c r="G30">
         <v>2024</v>
       </c>
+      <c r="H30" t="str">
+        <v>0502089697</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1120,10 +1211,13 @@
       <c r="G31">
         <v>2024</v>
       </c>
+      <c r="H31" t="str">
+        <v>0563190772</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H31"/>
   </ignoredErrors>
 </worksheet>
 </file>